--- a/Excel/Character.xlsx
+++ b/Excel/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24930" windowHeight="10730"/>
+    <workbookView windowWidth="24930" windowHeight="10130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Id</t>
   </si>
@@ -22,16 +22,19 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>STUN</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
     <t>HP</t>
-  </si>
-  <si>
-    <t>STUN</t>
-  </si>
-  <si>
-    <t>LP</t>
-  </si>
-  <si>
-    <t>MP</t>
   </si>
   <si>
     <t>LK</t>
@@ -1022,25 +1025,25 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1048,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -1089,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1130,7 +1133,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>950</v>
@@ -1171,7 +1174,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>850</v>
@@ -1212,7 +1215,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>1100</v>

--- a/Excel/Character.xlsx
+++ b/Excel/Character.xlsx
@@ -1066,7 +1066,7 @@
         <v>50</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="H2">
         <v>40</v>
@@ -1107,7 +1107,7 @@
         <v>60</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="H3">
         <v>30</v>
